--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,8 +778,16 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7000405</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,9 +784,1251 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135784622</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>353</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>414067</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6966257</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784622</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135784630</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>414080</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6966366</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784630</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135784624</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>414061</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6966238</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784624</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135784627</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>414083</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6966332</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784627</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135784623</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>414075</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6966258</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784623</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135784628</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>414097</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6966344</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784628</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135784619</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>414034</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6966236</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784619</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135784625</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>414064</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6966335</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784625</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135784621</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>414048</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6966257</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784621</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135784618</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>414032</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6966235</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784618</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135784617</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>414033</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6966234</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784617</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135784620</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92296</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6008693</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kritporing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Antrodia crassa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>414048</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6966257</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>För gammal fruktkropp för säker artbestämning.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784620</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135784620</v>
       </c>
       <c r="B14" t="n">
-        <v>92296</v>
+        <v>92298</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135784622</v>
       </c>
       <c r="B3" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135784619</v>
       </c>
       <c r="B9" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784625</v>
       </c>
       <c r="B10" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135784621</v>
       </c>
       <c r="B11" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784618</v>
       </c>
       <c r="B12" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>135784617</v>
       </c>
       <c r="B13" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135784620</v>
       </c>
       <c r="B14" t="n">
-        <v>92298</v>
+        <v>92312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135784622</v>
       </c>
       <c r="B3" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135784619</v>
       </c>
       <c r="B9" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784625</v>
       </c>
       <c r="B10" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135784621</v>
       </c>
       <c r="B11" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784618</v>
       </c>
       <c r="B12" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>135784617</v>
       </c>
       <c r="B13" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135784620</v>
       </c>
       <c r="B14" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135784620</v>
       </c>
       <c r="B14" t="n">
-        <v>92313</v>
+        <v>92314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135784622</v>
       </c>
       <c r="B3" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135784619</v>
       </c>
       <c r="B9" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784625</v>
       </c>
       <c r="B10" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135784621</v>
       </c>
       <c r="B11" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784618</v>
       </c>
       <c r="B12" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>135784617</v>
       </c>
       <c r="B13" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135784620</v>
       </c>
       <c r="B14" t="n">
-        <v>92314</v>
+        <v>92315</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135784622</v>
       </c>
       <c r="B3" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135784619</v>
       </c>
       <c r="B9" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784625</v>
       </c>
       <c r="B10" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135784621</v>
       </c>
       <c r="B11" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784618</v>
       </c>
       <c r="B12" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>135784617</v>
       </c>
       <c r="B13" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135784620</v>
       </c>
       <c r="B14" t="n">
-        <v>92315</v>
+        <v>92321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135784622</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135784619</v>
       </c>
       <c r="B9" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784625</v>
       </c>
       <c r="B10" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135784621</v>
       </c>
       <c r="B11" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784618</v>
       </c>
       <c r="B12" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>135784617</v>
       </c>
       <c r="B13" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135784620</v>
       </c>
       <c r="B14" t="n">
-        <v>92321</v>
+        <v>92322</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135784622</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135784619</v>
       </c>
       <c r="B9" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784625</v>
       </c>
       <c r="B10" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135784621</v>
       </c>
       <c r="B11" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784618</v>
       </c>
       <c r="B12" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>135784617</v>
       </c>
       <c r="B13" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135784620</v>
       </c>
       <c r="B14" t="n">
-        <v>92322</v>
+        <v>92328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135784622</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135784619</v>
       </c>
       <c r="B9" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135784625</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135784621</v>
       </c>
       <c r="B11" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135784618</v>
       </c>
       <c r="B12" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>135784617</v>
       </c>
       <c r="B13" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135784620</v>
       </c>
       <c r="B14" t="n">
-        <v>92328</v>
+        <v>92335</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>135784630</v>
       </c>
       <c r="B4" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135784624</v>
       </c>
       <c r="B5" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135784627</v>
       </c>
       <c r="B6" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>135784623</v>
       </c>
       <c r="B7" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135784628</v>
       </c>
       <c r="B8" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135784620</v>
       </c>
       <c r="B14" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 49573-2025 artfynd.xlsx
+++ b/artfynd/A 49573-2025 artfynd.xlsx
@@ -1911,7 +1911,7 @@
         <v>135784620</v>
       </c>
       <c r="B14" t="n">
-        <v>92336</v>
+        <v>92349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
